--- a/survey_templates/047_volunteer_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/047_volunteer_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>volunteer_type_choices</t>
+          <t>volunteer_position_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volunteer_type_choices</t>
+          <t>volunteer_position_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1203,63 +1203,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>volunteer_position_choices</t>
+          <t>feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Staff</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>volunteer_position_choices</t>
+          <t>feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>volunteer_position_choices</t>
+          <t>feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1271,63 +1271,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feedback_frequency_choices</t>
+          <t>submitted_by_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1339,63 +1339,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>user_1</t>
+          <t>user_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>User 1</t>
+          <t>User 4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>volunteer_program_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_2</t>
+          <t>program_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>User 2</t>
+          <t>Program 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>volunteer_program_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>user_3</t>
+          <t>program_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>User 3</t>
+          <t>Program 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submitted_by_choices</t>
+          <t>volunteer_program_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_4</t>
+          <t>program_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>User 4</t>
+          <t>Program 3</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>program_1</t>
+          <t>program_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Program 1</t>
+          <t>Program 4</t>
         </is>
       </c>
     </row>
@@ -1424,63 +1424,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>program_2</t>
+          <t>program_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Program 2</t>
+          <t>Program 5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>volunteer_program_choices</t>
+          <t>volunteer_location_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>program_3</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Program 3</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>volunteer_program_choices</t>
+          <t>volunteer_location_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>program_4</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Program 4</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>volunteer_program_choices</t>
+          <t>volunteer_location_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>program_5</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Program 5</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>location_1</t>
+          <t>location_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Location 1</t>
+          <t>Location 4</t>
         </is>
       </c>
     </row>
@@ -1509,63 +1509,63 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>location_2</t>
+          <t>location_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Location 2</t>
+          <t>Location 5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>volunteer_location_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>location_3</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Location 3</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>volunteer_location_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>location_4</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Location 4</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>volunteer_location_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>location_5</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Location 5</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
@@ -1577,63 +1577,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>tool_1</t>
+          <t>tool_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tool 1</t>
+          <t>Tool 4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>volunteer_committee_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>tool_2</t>
+          <t>committee_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tool 2</t>
+          <t>Committee 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>volunteer_committee_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>tool_3</t>
+          <t>committee_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tool 3</t>
+          <t>Committee 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>volunteer_committee_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>tool_4</t>
+          <t>committee_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tool 4</t>
+          <t>Committee 3</t>
         </is>
       </c>
     </row>
@@ -1645,148 +1645,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>committee_1</t>
+          <t>committee_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Committee 1</t>
+          <t>Committee 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>volunteer_committee_choices</t>
+          <t>submitted_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>committee_2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Committee 2</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>volunteer_committee_choices</t>
+          <t>submitted_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>committee_3</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Committee 3</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>volunteer_committee_choices</t>
+          <t>volunteer_status_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>committee_4</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Committee 4</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>volunteer_status_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>volunteer_status_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>volunteer_status_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>volunteer_status_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>volunteer_status_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -1798,61 +1798,10 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>user_1</t>
+          <t>user_4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>User 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>user_2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>User 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>user_3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>User 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>user_4</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>User 4</t>
         </is>
